--- a/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
+++ b/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
@@ -1829,13 +1829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0764FB6B-58D7-4652-93E6-C87D589CBFFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21923E02-A6AB-4547-A6FA-4B68793D2AEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4216DD43-E79F-411C-8DA5-5C4C93475CAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB80E634-C871-47D1-B45B-D4EA5A605E70}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7929D54D-A944-43CE-864F-BA188734B57B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEC692F-466A-4586-A619-FBB337963BBD}"/>
 </file>
--- a/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
+++ b/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
@@ -1829,13 +1829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21923E02-A6AB-4547-A6FA-4B68793D2AEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE038E6D-B8A2-4EFA-8A4F-FACBA1D9829F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB80E634-C871-47D1-B45B-D4EA5A605E70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4DF835-26DF-4A56-8C09-CA59904E4517}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEC692F-466A-4586-A619-FBB337963BBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6930F06-F151-4862-BEAD-63164FC987ED}"/>
 </file>
--- a/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
+++ b/ksoft_old/docs/records/Volume_Types_FT0305.xlsx
@@ -1829,13 +1829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE038E6D-B8A2-4EFA-8A4F-FACBA1D9829F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0764FB6B-58D7-4652-93E6-C87D589CBFFE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4DF835-26DF-4A56-8C09-CA59904E4517}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4216DD43-E79F-411C-8DA5-5C4C93475CAF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6930F06-F151-4862-BEAD-63164FC987ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7929D54D-A944-43CE-864F-BA188734B57B}"/>
 </file>